--- a/artfynd/A 59725-2025 artfynd.xlsx
+++ b/artfynd/A 59725-2025 artfynd.xlsx
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130080644</v>
+        <v>130080715</v>
       </c>
       <c r="B6" t="n">
-        <v>4773</v>
+        <v>5197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100299</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>352049</v>
+        <v>352047</v>
       </c>
       <c r="R6" t="n">
-        <v>6625465</v>
+        <v>6625255</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130080693</v>
+        <v>130080644</v>
       </c>
       <c r="B7" t="n">
-        <v>101004</v>
+        <v>4773</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>351872</v>
+        <v>352049</v>
       </c>
       <c r="R7" t="n">
-        <v>6625323</v>
+        <v>6625465</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130080664</v>
+        <v>130080678</v>
       </c>
       <c r="B8" t="n">
         <v>101004</v>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>352009</v>
+        <v>351989</v>
       </c>
       <c r="R8" t="n">
-        <v>6625188</v>
+        <v>6625211</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130080715</v>
+        <v>130080664</v>
       </c>
       <c r="B9" t="n">
-        <v>5197</v>
+        <v>101004</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1428,21 +1428,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>352047</v>
+        <v>352009</v>
       </c>
       <c r="R9" t="n">
-        <v>6625255</v>
+        <v>6625188</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130080678</v>
+        <v>130080693</v>
       </c>
       <c r="B10" t="n">
         <v>101004</v>
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>351989</v>
+        <v>351872</v>
       </c>
       <c r="R10" t="n">
-        <v>6625211</v>
+        <v>6625323</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130080665</v>
+        <v>130080742</v>
       </c>
       <c r="B12" t="n">
-        <v>101004</v>
+        <v>5197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>351806</v>
+        <v>352129</v>
       </c>
       <c r="R12" t="n">
-        <v>6625305</v>
+        <v>6625324</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130080742</v>
+        <v>130080665</v>
       </c>
       <c r="B13" t="n">
-        <v>5197</v>
+        <v>101004</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,21 +1852,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>352129</v>
+        <v>351806</v>
       </c>
       <c r="R13" t="n">
-        <v>6625324</v>
+        <v>6625305</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2265,32 +2265,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130080718</v>
+        <v>130080673</v>
       </c>
       <c r="B17" t="n">
-        <v>92943</v>
+        <v>101004</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>351953</v>
+        <v>351941</v>
       </c>
       <c r="R17" t="n">
-        <v>6625332</v>
+        <v>6625194</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2371,32 +2371,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130080673</v>
+        <v>130080718</v>
       </c>
       <c r="B18" t="n">
-        <v>101004</v>
+        <v>92943</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>351941</v>
+        <v>351953</v>
       </c>
       <c r="R18" t="n">
-        <v>6625194</v>
+        <v>6625332</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130080646</v>
+        <v>130080710</v>
       </c>
       <c r="B19" t="n">
-        <v>101004</v>
+        <v>92905</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2488,21 +2488,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>351958</v>
+        <v>351943</v>
       </c>
       <c r="R19" t="n">
-        <v>6625185</v>
+        <v>6625324</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130080710</v>
+        <v>130080646</v>
       </c>
       <c r="B20" t="n">
-        <v>92905</v>
+        <v>101004</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2594,21 +2594,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2618,10 +2618,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>351943</v>
+        <v>351958</v>
       </c>
       <c r="R20" t="n">
-        <v>6625324</v>
+        <v>6625185</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130080684</v>
+        <v>130080709</v>
       </c>
       <c r="B24" t="n">
-        <v>101004</v>
+        <v>91053</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3018,21 +3018,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>352014</v>
+        <v>351843</v>
       </c>
       <c r="R24" t="n">
-        <v>6625206</v>
+        <v>6625177</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3113,7 +3113,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130080695</v>
+        <v>130080653</v>
       </c>
       <c r="B25" t="n">
         <v>101004</v>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>351845</v>
+        <v>351849</v>
       </c>
       <c r="R25" t="n">
-        <v>6625269</v>
+        <v>6625259</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3219,10 +3219,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130080709</v>
+        <v>130080695</v>
       </c>
       <c r="B26" t="n">
-        <v>91053</v>
+        <v>101004</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3230,21 +3230,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4189</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>351843</v>
+        <v>351845</v>
       </c>
       <c r="R26" t="n">
-        <v>6625177</v>
+        <v>6625269</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3325,7 +3325,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130080653</v>
+        <v>130080684</v>
       </c>
       <c r="B27" t="n">
         <v>101004</v>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>351849</v>
+        <v>352014</v>
       </c>
       <c r="R27" t="n">
-        <v>6625259</v>
+        <v>6625206</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3961,7 +3961,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130080743</v>
+        <v>130080754</v>
       </c>
       <c r="B33" t="n">
         <v>101004</v>
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>351863</v>
+        <v>351994</v>
       </c>
       <c r="R33" t="n">
-        <v>6625270</v>
+        <v>6625214</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4067,7 +4067,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130080754</v>
+        <v>130080659</v>
       </c>
       <c r="B34" t="n">
         <v>101004</v>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>351994</v>
+        <v>351978</v>
       </c>
       <c r="R34" t="n">
-        <v>6625214</v>
+        <v>6625180</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4173,7 +4173,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130080659</v>
+        <v>130080668</v>
       </c>
       <c r="B35" t="n">
         <v>101004</v>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>351978</v>
+        <v>352009</v>
       </c>
       <c r="R35" t="n">
-        <v>6625180</v>
+        <v>6625177</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4279,32 +4279,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130080705</v>
+        <v>130080722</v>
       </c>
       <c r="B36" t="n">
-        <v>92943</v>
+        <v>101004</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4314,13 +4314,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>351964</v>
+        <v>351871</v>
       </c>
       <c r="R36" t="n">
-        <v>6625310</v>
+        <v>6625188</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130080668</v>
+        <v>130080746</v>
       </c>
       <c r="B37" t="n">
         <v>101004</v>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>352009</v>
+        <v>351961</v>
       </c>
       <c r="R37" t="n">
-        <v>6625177</v>
+        <v>6625364</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4491,7 +4491,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130080746</v>
+        <v>130080743</v>
       </c>
       <c r="B38" t="n">
         <v>101004</v>
@@ -4526,10 +4526,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>351961</v>
+        <v>351863</v>
       </c>
       <c r="R38" t="n">
-        <v>6625364</v>
+        <v>6625270</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4703,32 +4703,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130080722</v>
+        <v>130080705</v>
       </c>
       <c r="B40" t="n">
-        <v>101004</v>
+        <v>92943</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4738,13 +4738,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>351871</v>
+        <v>351964</v>
       </c>
       <c r="R40" t="n">
-        <v>6625188</v>
+        <v>6625310</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4809,10 +4809,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130080692</v>
+        <v>130080731</v>
       </c>
       <c r="B41" t="n">
-        <v>101004</v>
+        <v>5197</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4844,10 +4844,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>351814</v>
+        <v>352108</v>
       </c>
       <c r="R41" t="n">
-        <v>6625310</v>
+        <v>6625477</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4915,7 +4915,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130080731</v>
+        <v>130080702</v>
       </c>
       <c r="B42" t="n">
         <v>5197</v>
@@ -4950,10 +4950,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>352108</v>
+        <v>352012</v>
       </c>
       <c r="R42" t="n">
-        <v>6625477</v>
+        <v>6625262</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5021,10 +5021,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130080702</v>
+        <v>130080700</v>
       </c>
       <c r="B43" t="n">
-        <v>5197</v>
+        <v>101004</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5032,21 +5032,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5056,13 +5056,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>352012</v>
+        <v>351954</v>
       </c>
       <c r="R43" t="n">
-        <v>6625262</v>
+        <v>6625185</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130080700</v>
+        <v>130080692</v>
       </c>
       <c r="B44" t="n">
         <v>101004</v>
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>351954</v>
+        <v>351814</v>
       </c>
       <c r="R44" t="n">
-        <v>6625185</v>
+        <v>6625310</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5551,32 +5551,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130080658</v>
+        <v>130080688</v>
       </c>
       <c r="B48" t="n">
-        <v>80229</v>
+        <v>92943</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6463</v>
+        <v>5966</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5586,13 +5586,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>352098</v>
+        <v>351946</v>
       </c>
       <c r="R48" t="n">
-        <v>6625401</v>
+        <v>6625322</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130080677</v>
+        <v>130080658</v>
       </c>
       <c r="B49" t="n">
-        <v>101004</v>
+        <v>80229</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5668,21 +5668,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>6463</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5692,13 +5692,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>351993</v>
+        <v>352098</v>
       </c>
       <c r="R49" t="n">
-        <v>6625176</v>
+        <v>6625401</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5869,32 +5869,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130080688</v>
+        <v>130080744</v>
       </c>
       <c r="B51" t="n">
-        <v>92943</v>
+        <v>101004</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5904,13 +5904,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>351946</v>
+        <v>352017</v>
       </c>
       <c r="R51" t="n">
-        <v>6625322</v>
+        <v>6625252</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130080744</v>
+        <v>130080677</v>
       </c>
       <c r="B52" t="n">
         <v>101004</v>
@@ -6010,13 +6010,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>352017</v>
+        <v>351993</v>
       </c>
       <c r="R52" t="n">
-        <v>6625252</v>
+        <v>6625176</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130080680</v>
+        <v>130080690</v>
       </c>
       <c r="B54" t="n">
         <v>101004</v>
@@ -6222,13 +6222,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>351923</v>
+        <v>351880</v>
       </c>
       <c r="R54" t="n">
-        <v>6625280</v>
+        <v>6625196</v>
       </c>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130080690</v>
+        <v>130080680</v>
       </c>
       <c r="B55" t="n">
         <v>101004</v>
@@ -6328,13 +6328,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>351880</v>
+        <v>351923</v>
       </c>
       <c r="R55" t="n">
-        <v>6625196</v>
+        <v>6625280</v>
       </c>
       <c r="S55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6399,32 +6399,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130080748</v>
+        <v>130080711</v>
       </c>
       <c r="B56" t="n">
-        <v>101004</v>
+        <v>92943</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6434,10 +6434,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>351968</v>
+        <v>351948</v>
       </c>
       <c r="R56" t="n">
-        <v>6625362</v>
+        <v>6625339</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6505,32 +6505,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130080711</v>
+        <v>130080748</v>
       </c>
       <c r="B57" t="n">
-        <v>92943</v>
+        <v>101004</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6540,10 +6540,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>351948</v>
+        <v>351968</v>
       </c>
       <c r="R57" t="n">
-        <v>6625339</v>
+        <v>6625362</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6611,7 +6611,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130080747</v>
+        <v>130080724</v>
       </c>
       <c r="B58" t="n">
         <v>101004</v>
@@ -6646,10 +6646,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>351963</v>
+        <v>352010</v>
       </c>
       <c r="R58" t="n">
-        <v>6625354</v>
+        <v>6625223</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6717,10 +6717,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130080698</v>
+        <v>130080747</v>
       </c>
       <c r="B59" t="n">
-        <v>4773</v>
+        <v>101004</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6728,21 +6728,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100299</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6752,10 +6752,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>351986</v>
+        <v>351963</v>
       </c>
       <c r="R59" t="n">
-        <v>6625378</v>
+        <v>6625354</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6823,32 +6823,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130080652</v>
+        <v>130080698</v>
       </c>
       <c r="B60" t="n">
-        <v>92943</v>
+        <v>4773</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5966</v>
+        <v>100299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6858,10 +6858,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>351953</v>
+        <v>351986</v>
       </c>
       <c r="R60" t="n">
-        <v>6625320</v>
+        <v>6625378</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6929,32 +6929,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130080724</v>
+        <v>130080652</v>
       </c>
       <c r="B61" t="n">
-        <v>101004</v>
+        <v>92943</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>352010</v>
+        <v>351953</v>
       </c>
       <c r="R61" t="n">
-        <v>6625223</v>
+        <v>6625320</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>

--- a/artfynd/A 59725-2025 artfynd.xlsx
+++ b/artfynd/A 59725-2025 artfynd.xlsx
@@ -3537,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130080689</v>
+        <v>130080703</v>
       </c>
       <c r="B29" t="n">
-        <v>80068</v>
+        <v>40126</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3548,21 +3548,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6441</v>
+        <v>214803</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>352000</v>
+        <v>351947</v>
       </c>
       <c r="R29" t="n">
-        <v>6625332</v>
+        <v>6625286</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130080703</v>
+        <v>130080689</v>
       </c>
       <c r="B30" t="n">
-        <v>40126</v>
+        <v>80068</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3654,21 +3654,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>214803</v>
+        <v>6441</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>351947</v>
+        <v>352000</v>
       </c>
       <c r="R30" t="n">
-        <v>6625286</v>
+        <v>6625332</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -5551,32 +5551,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130080744</v>
+        <v>130080753</v>
       </c>
       <c r="B48" t="n">
-        <v>101020</v>
+        <v>57738</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5586,13 +5586,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>352017</v>
+        <v>351938</v>
       </c>
       <c r="R48" t="n">
-        <v>6625252</v>
+        <v>6625338</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130080677</v>
+        <v>130080658</v>
       </c>
       <c r="B49" t="n">
-        <v>101020</v>
+        <v>80235</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5668,21 +5668,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>6463</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5692,13 +5692,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>351993</v>
+        <v>352098</v>
       </c>
       <c r="R49" t="n">
-        <v>6625176</v>
+        <v>6625401</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5763,10 +5763,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130080753</v>
+        <v>130080688</v>
       </c>
       <c r="B50" t="n">
-        <v>57738</v>
+        <v>92959</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5774,21 +5774,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5798,10 +5798,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>351938</v>
+        <v>351946</v>
       </c>
       <c r="R50" t="n">
-        <v>6625338</v>
+        <v>6625322</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5869,10 +5869,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130080658</v>
+        <v>130080744</v>
       </c>
       <c r="B51" t="n">
-        <v>80235</v>
+        <v>101020</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5880,21 +5880,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6463</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5904,10 +5904,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>352098</v>
+        <v>352017</v>
       </c>
       <c r="R51" t="n">
-        <v>6625401</v>
+        <v>6625252</v>
       </c>
       <c r="S51" t="n">
         <v>6</v>
@@ -5975,32 +5975,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130080688</v>
+        <v>130080677</v>
       </c>
       <c r="B52" t="n">
-        <v>92959</v>
+        <v>101020</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6010,10 +6010,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>351946</v>
+        <v>351993</v>
       </c>
       <c r="R52" t="n">
-        <v>6625322</v>
+        <v>6625176</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6611,32 +6611,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130080652</v>
+        <v>130080698</v>
       </c>
       <c r="B58" t="n">
-        <v>92959</v>
+        <v>4773</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5966</v>
+        <v>100299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6646,10 +6646,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>351953</v>
+        <v>351986</v>
       </c>
       <c r="R58" t="n">
-        <v>6625320</v>
+        <v>6625378</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6717,32 +6717,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130080747</v>
+        <v>130080652</v>
       </c>
       <c r="B59" t="n">
-        <v>101020</v>
+        <v>92959</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6752,10 +6752,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>351963</v>
+        <v>351953</v>
       </c>
       <c r="R59" t="n">
-        <v>6625354</v>
+        <v>6625320</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6823,7 +6823,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130080724</v>
+        <v>130080747</v>
       </c>
       <c r="B60" t="n">
         <v>101020</v>
@@ -6858,10 +6858,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>352010</v>
+        <v>351963</v>
       </c>
       <c r="R60" t="n">
-        <v>6625223</v>
+        <v>6625354</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6929,10 +6929,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130080698</v>
+        <v>130080724</v>
       </c>
       <c r="B61" t="n">
-        <v>4773</v>
+        <v>101020</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100299</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>351986</v>
+        <v>352010</v>
       </c>
       <c r="R61" t="n">
-        <v>6625378</v>
+        <v>6625223</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>

--- a/artfynd/A 59725-2025 artfynd.xlsx
+++ b/artfynd/A 59725-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130080714</v>
+        <v>130080721</v>
       </c>
       <c r="B2" t="n">
-        <v>101020</v>
+        <v>91603</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>352013</v>
+        <v>351857</v>
       </c>
       <c r="R2" t="n">
-        <v>6625233</v>
+        <v>6625260</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130080721</v>
+        <v>130080714</v>
       </c>
       <c r="B3" t="n">
-        <v>91603</v>
+        <v>101020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>351857</v>
+        <v>352013</v>
       </c>
       <c r="R3" t="n">
-        <v>6625260</v>
+        <v>6625233</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130080737</v>
+        <v>130080644</v>
       </c>
       <c r="B5" t="n">
-        <v>79095</v>
+        <v>4773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>351971</v>
+        <v>352049</v>
       </c>
       <c r="R5" t="n">
-        <v>6625428</v>
+        <v>6625465</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130080644</v>
+        <v>130080737</v>
       </c>
       <c r="B6" t="n">
-        <v>4773</v>
+        <v>79095</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>352049</v>
+        <v>351971</v>
       </c>
       <c r="R6" t="n">
-        <v>6625465</v>
+        <v>6625428</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130080665</v>
+        <v>130080742</v>
       </c>
       <c r="B11" t="n">
-        <v>101020</v>
+        <v>5197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1640,21 +1640,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>351806</v>
+        <v>352129</v>
       </c>
       <c r="R11" t="n">
-        <v>6625305</v>
+        <v>6625324</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130080730</v>
+        <v>130080672</v>
       </c>
       <c r="B12" t="n">
-        <v>101020</v>
+        <v>8440</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>351959</v>
+        <v>351844</v>
       </c>
       <c r="R12" t="n">
-        <v>6625368</v>
+        <v>6625206</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130080742</v>
+        <v>130080665</v>
       </c>
       <c r="B13" t="n">
-        <v>5197</v>
+        <v>101020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,21 +1852,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>352129</v>
+        <v>351806</v>
       </c>
       <c r="R13" t="n">
-        <v>6625324</v>
+        <v>6625305</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130080672</v>
+        <v>130080730</v>
       </c>
       <c r="B14" t="n">
-        <v>8440</v>
+        <v>101020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,21 +1958,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>351844</v>
+        <v>351959</v>
       </c>
       <c r="R14" t="n">
-        <v>6625206</v>
+        <v>6625368</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -3537,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130080703</v>
+        <v>130080689</v>
       </c>
       <c r="B29" t="n">
-        <v>40126</v>
+        <v>80068</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3548,21 +3548,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>214803</v>
+        <v>6441</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>351947</v>
+        <v>352000</v>
       </c>
       <c r="R29" t="n">
-        <v>6625286</v>
+        <v>6625332</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130080689</v>
+        <v>130080703</v>
       </c>
       <c r="B30" t="n">
-        <v>80068</v>
+        <v>40126</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3654,21 +3654,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6441</v>
+        <v>214803</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>352000</v>
+        <v>351947</v>
       </c>
       <c r="R30" t="n">
-        <v>6625332</v>
+        <v>6625286</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -5551,32 +5551,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130080753</v>
+        <v>130080744</v>
       </c>
       <c r="B48" t="n">
-        <v>57738</v>
+        <v>101020</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5586,13 +5586,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>351938</v>
+        <v>352017</v>
       </c>
       <c r="R48" t="n">
-        <v>6625338</v>
+        <v>6625252</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130080658</v>
+        <v>130080677</v>
       </c>
       <c r="B49" t="n">
-        <v>80235</v>
+        <v>101020</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5668,21 +5668,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6463</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5692,13 +5692,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>352098</v>
+        <v>351993</v>
       </c>
       <c r="R49" t="n">
-        <v>6625401</v>
+        <v>6625176</v>
       </c>
       <c r="S49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5763,10 +5763,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130080688</v>
+        <v>130080753</v>
       </c>
       <c r="B50" t="n">
-        <v>92959</v>
+        <v>57738</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5774,21 +5774,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5798,10 +5798,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>351946</v>
+        <v>351938</v>
       </c>
       <c r="R50" t="n">
-        <v>6625322</v>
+        <v>6625338</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5869,10 +5869,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130080744</v>
+        <v>130080658</v>
       </c>
       <c r="B51" t="n">
-        <v>101020</v>
+        <v>80235</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5880,21 +5880,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>6463</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5904,10 +5904,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>352017</v>
+        <v>352098</v>
       </c>
       <c r="R51" t="n">
-        <v>6625252</v>
+        <v>6625401</v>
       </c>
       <c r="S51" t="n">
         <v>6</v>
@@ -5975,32 +5975,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130080677</v>
+        <v>130080688</v>
       </c>
       <c r="B52" t="n">
-        <v>101020</v>
+        <v>92959</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6010,10 +6010,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>351993</v>
+        <v>351946</v>
       </c>
       <c r="R52" t="n">
-        <v>6625176</v>
+        <v>6625322</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>

--- a/artfynd/A 59725-2025 artfynd.xlsx
+++ b/artfynd/A 59725-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130080721</v>
       </c>
       <c r="B2" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>130080714</v>
       </c>
       <c r="B3" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130080715</v>
+        <v>130080693</v>
       </c>
       <c r="B7" t="n">
-        <v>5197</v>
+        <v>101022</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>352047</v>
+        <v>351872</v>
       </c>
       <c r="R7" t="n">
-        <v>6625255</v>
+        <v>6625323</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130080693</v>
+        <v>130080678</v>
       </c>
       <c r="B8" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>351872</v>
+        <v>351989</v>
       </c>
       <c r="R8" t="n">
-        <v>6625323</v>
+        <v>6625211</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130080678</v>
+        <v>130080664</v>
       </c>
       <c r="B9" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>351989</v>
+        <v>352009</v>
       </c>
       <c r="R9" t="n">
-        <v>6625211</v>
+        <v>6625188</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130080664</v>
+        <v>130080715</v>
       </c>
       <c r="B10" t="n">
-        <v>101020</v>
+        <v>5197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1534,21 +1534,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>352009</v>
+        <v>352047</v>
       </c>
       <c r="R10" t="n">
-        <v>6625188</v>
+        <v>6625255</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130080742</v>
+        <v>130080672</v>
       </c>
       <c r="B11" t="n">
-        <v>5197</v>
+        <v>8440</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1640,21 +1640,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>352129</v>
+        <v>351844</v>
       </c>
       <c r="R11" t="n">
-        <v>6625324</v>
+        <v>6625206</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130080672</v>
+        <v>130080742</v>
       </c>
       <c r="B12" t="n">
-        <v>8440</v>
+        <v>5197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>351844</v>
+        <v>352129</v>
       </c>
       <c r="R12" t="n">
-        <v>6625206</v>
+        <v>6625324</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1844,7 +1844,7 @@
         <v>130080665</v>
       </c>
       <c r="B13" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>130080730</v>
       </c>
       <c r="B14" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>130080691</v>
       </c>
       <c r="B15" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>130080660</v>
       </c>
       <c r="B16" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2265,32 +2265,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130080718</v>
+        <v>130080673</v>
       </c>
       <c r="B17" t="n">
-        <v>92959</v>
+        <v>101022</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>351953</v>
+        <v>351941</v>
       </c>
       <c r="R17" t="n">
-        <v>6625332</v>
+        <v>6625194</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2371,32 +2371,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130080673</v>
+        <v>130080718</v>
       </c>
       <c r="B18" t="n">
-        <v>101020</v>
+        <v>92961</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>351941</v>
+        <v>351953</v>
       </c>
       <c r="R18" t="n">
-        <v>6625194</v>
+        <v>6625332</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2480,7 +2480,7 @@
         <v>130080710</v>
       </c>
       <c r="B19" t="n">
-        <v>92921</v>
+        <v>92923</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>130080646</v>
       </c>
       <c r="B20" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>130080729</v>
       </c>
       <c r="B21" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>130080745</v>
       </c>
       <c r="B22" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>130080667</v>
       </c>
       <c r="B23" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>130080709</v>
       </c>
       <c r="B24" t="n">
-        <v>91069</v>
+        <v>91071</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3113,32 +3113,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130080653</v>
+        <v>130080727</v>
       </c>
       <c r="B25" t="n">
-        <v>101020</v>
+        <v>92961</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3148,13 +3148,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>351849</v>
+        <v>351974</v>
       </c>
       <c r="R25" t="n">
-        <v>6625259</v>
+        <v>6625448</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3219,10 +3219,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130080695</v>
+        <v>130080653</v>
       </c>
       <c r="B26" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>351845</v>
+        <v>351849</v>
       </c>
       <c r="R26" t="n">
-        <v>6625269</v>
+        <v>6625259</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3325,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130080684</v>
+        <v>130080695</v>
       </c>
       <c r="B27" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>352014</v>
+        <v>351845</v>
       </c>
       <c r="R27" t="n">
-        <v>6625206</v>
+        <v>6625269</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3431,32 +3431,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130080727</v>
+        <v>130080684</v>
       </c>
       <c r="B28" t="n">
-        <v>92959</v>
+        <v>101022</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3466,13 +3466,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>351974</v>
+        <v>352014</v>
       </c>
       <c r="R28" t="n">
-        <v>6625448</v>
+        <v>6625206</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>130080706</v>
       </c>
       <c r="B31" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3855,32 +3855,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130080705</v>
+        <v>130080722</v>
       </c>
       <c r="B32" t="n">
-        <v>92959</v>
+        <v>101022</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3890,13 +3890,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>351964</v>
+        <v>351871</v>
       </c>
       <c r="R32" t="n">
-        <v>6625310</v>
+        <v>6625188</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>130080707</v>
       </c>
       <c r="B33" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>130080754</v>
       </c>
       <c r="B34" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4173,10 +4173,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130080659</v>
+        <v>130080668</v>
       </c>
       <c r="B35" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>351978</v>
+        <v>352009</v>
       </c>
       <c r="R35" t="n">
-        <v>6625180</v>
+        <v>6625177</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4279,10 +4279,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130080668</v>
+        <v>130080746</v>
       </c>
       <c r="B36" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>352009</v>
+        <v>351961</v>
       </c>
       <c r="R36" t="n">
-        <v>6625177</v>
+        <v>6625364</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4385,10 +4385,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130080722</v>
+        <v>130080743</v>
       </c>
       <c r="B37" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>351871</v>
+        <v>351863</v>
       </c>
       <c r="R37" t="n">
-        <v>6625188</v>
+        <v>6625270</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4491,32 +4491,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130080746</v>
+        <v>130080705</v>
       </c>
       <c r="B38" t="n">
-        <v>101020</v>
+        <v>92961</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4526,13 +4526,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>351961</v>
+        <v>351964</v>
       </c>
       <c r="R38" t="n">
-        <v>6625364</v>
+        <v>6625310</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4597,10 +4597,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130080743</v>
+        <v>130080659</v>
       </c>
       <c r="B39" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4632,10 +4632,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>351863</v>
+        <v>351978</v>
       </c>
       <c r="R39" t="n">
-        <v>6625270</v>
+        <v>6625180</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4706,7 +4706,7 @@
         <v>130080719</v>
       </c>
       <c r="B40" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>130080700</v>
       </c>
       <c r="B43" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>130080692</v>
       </c>
       <c r="B44" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>130080661</v>
       </c>
       <c r="B46" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>130080732</v>
       </c>
       <c r="B47" t="n">
-        <v>92959</v>
+        <v>92961</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5551,32 +5551,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130080744</v>
+        <v>130080688</v>
       </c>
       <c r="B48" t="n">
-        <v>101020</v>
+        <v>92961</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5586,13 +5586,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>352017</v>
+        <v>351946</v>
       </c>
       <c r="R48" t="n">
-        <v>6625252</v>
+        <v>6625322</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5657,32 +5657,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130080677</v>
+        <v>130080753</v>
       </c>
       <c r="B49" t="n">
-        <v>101020</v>
+        <v>57738</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5692,10 +5692,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>351993</v>
+        <v>351938</v>
       </c>
       <c r="R49" t="n">
-        <v>6625176</v>
+        <v>6625338</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5763,32 +5763,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130080753</v>
+        <v>130080658</v>
       </c>
       <c r="B50" t="n">
-        <v>57738</v>
+        <v>80235</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5798,13 +5798,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>351938</v>
+        <v>352098</v>
       </c>
       <c r="R50" t="n">
-        <v>6625338</v>
+        <v>6625401</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5869,10 +5869,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130080658</v>
+        <v>130080677</v>
       </c>
       <c r="B51" t="n">
-        <v>80235</v>
+        <v>101022</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5880,21 +5880,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6463</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5904,13 +5904,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>352098</v>
+        <v>351993</v>
       </c>
       <c r="R51" t="n">
-        <v>6625401</v>
+        <v>6625176</v>
       </c>
       <c r="S51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5975,32 +5975,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130080688</v>
+        <v>130080744</v>
       </c>
       <c r="B52" t="n">
-        <v>92959</v>
+        <v>101022</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6010,13 +6010,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>351946</v>
+        <v>352017</v>
       </c>
       <c r="R52" t="n">
-        <v>6625322</v>
+        <v>6625252</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6081,10 +6081,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130080649</v>
+        <v>130080680</v>
       </c>
       <c r="B53" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6116,13 +6116,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>351813</v>
+        <v>351923</v>
       </c>
       <c r="R53" t="n">
-        <v>6625308</v>
+        <v>6625280</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6187,10 +6187,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130080690</v>
+        <v>130080649</v>
       </c>
       <c r="B54" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6222,13 +6222,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>351880</v>
+        <v>351813</v>
       </c>
       <c r="R54" t="n">
-        <v>6625196</v>
+        <v>6625308</v>
       </c>
       <c r="S54" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6293,10 +6293,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130080680</v>
+        <v>130080690</v>
       </c>
       <c r="B55" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6328,13 +6328,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>351923</v>
+        <v>351880</v>
       </c>
       <c r="R55" t="n">
-        <v>6625280</v>
+        <v>6625196</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6399,32 +6399,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130080711</v>
+        <v>130080748</v>
       </c>
       <c r="B56" t="n">
-        <v>92959</v>
+        <v>101022</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6434,10 +6434,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>351948</v>
+        <v>351968</v>
       </c>
       <c r="R56" t="n">
-        <v>6625339</v>
+        <v>6625362</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6505,32 +6505,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130080748</v>
+        <v>130080711</v>
       </c>
       <c r="B57" t="n">
-        <v>101020</v>
+        <v>92961</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6540,10 +6540,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>351968</v>
+        <v>351948</v>
       </c>
       <c r="R57" t="n">
-        <v>6625362</v>
+        <v>6625339</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6720,7 +6720,7 @@
         <v>130080652</v>
       </c>
       <c r="B59" t="n">
-        <v>92959</v>
+        <v>92961</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6826,7 +6826,7 @@
         <v>130080747</v>
       </c>
       <c r="B60" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         <v>130080724</v>
       </c>
       <c r="B61" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 59725-2025 artfynd.xlsx
+++ b/artfynd/A 59725-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130080721</v>
+        <v>130080714</v>
       </c>
       <c r="B2" t="n">
-        <v>91605</v>
+        <v>101109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>351857</v>
+        <v>352013</v>
       </c>
       <c r="R2" t="n">
-        <v>6625260</v>
+        <v>6625233</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130080714</v>
+        <v>130080721</v>
       </c>
       <c r="B3" t="n">
-        <v>101022</v>
+        <v>91692</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>352013</v>
+        <v>351857</v>
       </c>
       <c r="R3" t="n">
-        <v>6625233</v>
+        <v>6625260</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -890,7 +890,7 @@
         <v>130080681</v>
       </c>
       <c r="B4" t="n">
-        <v>80235</v>
+        <v>80320</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130080644</v>
+        <v>130080737</v>
       </c>
       <c r="B5" t="n">
-        <v>4773</v>
+        <v>79180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>352049</v>
+        <v>351971</v>
       </c>
       <c r="R5" t="n">
-        <v>6625465</v>
+        <v>6625428</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130080737</v>
+        <v>130080644</v>
       </c>
       <c r="B6" t="n">
-        <v>79095</v>
+        <v>4773</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>351971</v>
+        <v>352049</v>
       </c>
       <c r="R6" t="n">
-        <v>6625428</v>
+        <v>6625465</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130080693</v>
+        <v>130080678</v>
       </c>
       <c r="B7" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>351872</v>
+        <v>351989</v>
       </c>
       <c r="R7" t="n">
-        <v>6625323</v>
+        <v>6625211</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130080678</v>
+        <v>130080693</v>
       </c>
       <c r="B8" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>351989</v>
+        <v>351872</v>
       </c>
       <c r="R8" t="n">
-        <v>6625211</v>
+        <v>6625323</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130080664</v>
+        <v>130080715</v>
       </c>
       <c r="B9" t="n">
-        <v>101022</v>
+        <v>5197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1428,21 +1428,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>352009</v>
+        <v>352047</v>
       </c>
       <c r="R9" t="n">
-        <v>6625188</v>
+        <v>6625255</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130080715</v>
+        <v>130080664</v>
       </c>
       <c r="B10" t="n">
-        <v>5197</v>
+        <v>101109</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1534,21 +1534,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>352047</v>
+        <v>352009</v>
       </c>
       <c r="R10" t="n">
-        <v>6625255</v>
+        <v>6625188</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130080672</v>
+        <v>130080730</v>
       </c>
       <c r="B11" t="n">
-        <v>8440</v>
+        <v>101109</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1640,21 +1640,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>351844</v>
+        <v>351959</v>
       </c>
       <c r="R11" t="n">
-        <v>6625206</v>
+        <v>6625368</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1844,7 +1844,7 @@
         <v>130080665</v>
       </c>
       <c r="B13" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130080730</v>
+        <v>130080672</v>
       </c>
       <c r="B14" t="n">
-        <v>101022</v>
+        <v>8440</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,21 +1958,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>351959</v>
+        <v>351844</v>
       </c>
       <c r="R14" t="n">
-        <v>6625368</v>
+        <v>6625206</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130080691</v>
+        <v>130080660</v>
       </c>
       <c r="B15" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>351862</v>
+        <v>351973</v>
       </c>
       <c r="R15" t="n">
-        <v>6625186</v>
+        <v>6625359</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130080660</v>
+        <v>130080691</v>
       </c>
       <c r="B16" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>351973</v>
+        <v>351862</v>
       </c>
       <c r="R16" t="n">
-        <v>6625359</v>
+        <v>6625186</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2268,7 +2268,7 @@
         <v>130080673</v>
       </c>
       <c r="B17" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>130080718</v>
       </c>
       <c r="B18" t="n">
-        <v>92961</v>
+        <v>93048</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130080710</v>
+        <v>130080646</v>
       </c>
       <c r="B19" t="n">
-        <v>92923</v>
+        <v>101109</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2488,21 +2488,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>351943</v>
+        <v>351958</v>
       </c>
       <c r="R19" t="n">
-        <v>6625324</v>
+        <v>6625185</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130080646</v>
+        <v>130080710</v>
       </c>
       <c r="B20" t="n">
-        <v>101022</v>
+        <v>93010</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2594,21 +2594,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2618,10 +2618,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>351958</v>
+        <v>351943</v>
       </c>
       <c r="R20" t="n">
-        <v>6625185</v>
+        <v>6625324</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2692,7 +2692,7 @@
         <v>130080729</v>
       </c>
       <c r="B21" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>130080745</v>
       </c>
       <c r="B22" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>130080667</v>
       </c>
       <c r="B23" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130080709</v>
+        <v>130080695</v>
       </c>
       <c r="B24" t="n">
-        <v>91071</v>
+        <v>101109</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3018,21 +3018,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4189</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>351843</v>
+        <v>351845</v>
       </c>
       <c r="R24" t="n">
-        <v>6625177</v>
+        <v>6625269</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3113,32 +3113,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130080727</v>
+        <v>130080684</v>
       </c>
       <c r="B25" t="n">
-        <v>92961</v>
+        <v>101109</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3148,13 +3148,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>351974</v>
+        <v>352014</v>
       </c>
       <c r="R25" t="n">
-        <v>6625448</v>
+        <v>6625206</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3219,32 +3219,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130080653</v>
+        <v>130080727</v>
       </c>
       <c r="B26" t="n">
-        <v>101022</v>
+        <v>93048</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3254,13 +3254,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>351849</v>
+        <v>351974</v>
       </c>
       <c r="R26" t="n">
-        <v>6625259</v>
+        <v>6625448</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3325,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130080695</v>
+        <v>130080653</v>
       </c>
       <c r="B27" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>351845</v>
+        <v>351849</v>
       </c>
       <c r="R27" t="n">
-        <v>6625269</v>
+        <v>6625259</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3431,10 +3431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130080684</v>
+        <v>130080709</v>
       </c>
       <c r="B28" t="n">
-        <v>101022</v>
+        <v>91158</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,21 +3442,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>352014</v>
+        <v>351843</v>
       </c>
       <c r="R28" t="n">
-        <v>6625206</v>
+        <v>6625177</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3537,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130080689</v>
+        <v>130080703</v>
       </c>
       <c r="B29" t="n">
-        <v>80068</v>
+        <v>40211</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3548,21 +3548,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6441</v>
+        <v>214803</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>352000</v>
+        <v>351947</v>
       </c>
       <c r="R29" t="n">
-        <v>6625332</v>
+        <v>6625286</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130080703</v>
+        <v>130080689</v>
       </c>
       <c r="B30" t="n">
-        <v>40126</v>
+        <v>80153</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3654,21 +3654,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>214803</v>
+        <v>6441</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>351947</v>
+        <v>352000</v>
       </c>
       <c r="R30" t="n">
-        <v>6625286</v>
+        <v>6625332</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3752,7 +3752,7 @@
         <v>130080706</v>
       </c>
       <c r="B31" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3855,10 +3855,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130080722</v>
+        <v>130080754</v>
       </c>
       <c r="B32" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>351871</v>
+        <v>351994</v>
       </c>
       <c r="R32" t="n">
-        <v>6625188</v>
+        <v>6625214</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3961,10 +3961,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130080707</v>
+        <v>130080743</v>
       </c>
       <c r="B33" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>351988</v>
+        <v>351863</v>
       </c>
       <c r="R33" t="n">
-        <v>6625206</v>
+        <v>6625270</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4067,10 +4067,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130080754</v>
+        <v>130080719</v>
       </c>
       <c r="B34" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>351994</v>
+        <v>351983</v>
       </c>
       <c r="R34" t="n">
-        <v>6625214</v>
+        <v>6625356</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4173,32 +4173,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130080668</v>
+        <v>130080705</v>
       </c>
       <c r="B35" t="n">
-        <v>101022</v>
+        <v>93048</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4208,13 +4208,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>352009</v>
+        <v>351964</v>
       </c>
       <c r="R35" t="n">
-        <v>6625177</v>
+        <v>6625310</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4279,10 +4279,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130080746</v>
+        <v>130080668</v>
       </c>
       <c r="B36" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>351961</v>
+        <v>352009</v>
       </c>
       <c r="R36" t="n">
-        <v>6625364</v>
+        <v>6625177</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4385,10 +4385,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130080743</v>
+        <v>130080707</v>
       </c>
       <c r="B37" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>351863</v>
+        <v>351988</v>
       </c>
       <c r="R37" t="n">
-        <v>6625270</v>
+        <v>6625206</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4491,32 +4491,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130080705</v>
+        <v>130080659</v>
       </c>
       <c r="B38" t="n">
-        <v>92961</v>
+        <v>101109</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4526,13 +4526,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>351964</v>
+        <v>351978</v>
       </c>
       <c r="R38" t="n">
-        <v>6625310</v>
+        <v>6625180</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4597,10 +4597,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130080659</v>
+        <v>130080722</v>
       </c>
       <c r="B39" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4632,10 +4632,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>351978</v>
+        <v>351871</v>
       </c>
       <c r="R39" t="n">
-        <v>6625180</v>
+        <v>6625188</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4703,10 +4703,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130080719</v>
+        <v>130080746</v>
       </c>
       <c r="B40" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4738,10 +4738,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>351983</v>
+        <v>351961</v>
       </c>
       <c r="R40" t="n">
-        <v>6625356</v>
+        <v>6625364</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4809,10 +4809,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130080731</v>
+        <v>130080700</v>
       </c>
       <c r="B41" t="n">
-        <v>5197</v>
+        <v>101109</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4844,13 +4844,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>352108</v>
+        <v>351954</v>
       </c>
       <c r="R41" t="n">
-        <v>6625477</v>
+        <v>6625185</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130080702</v>
+        <v>130080731</v>
       </c>
       <c r="B42" t="n">
         <v>5197</v>
@@ -4950,10 +4950,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>352012</v>
+        <v>352108</v>
       </c>
       <c r="R42" t="n">
-        <v>6625262</v>
+        <v>6625477</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5021,10 +5021,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130080700</v>
+        <v>130080702</v>
       </c>
       <c r="B43" t="n">
-        <v>101022</v>
+        <v>5197</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5032,21 +5032,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5056,13 +5056,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>351954</v>
+        <v>352012</v>
       </c>
       <c r="R43" t="n">
-        <v>6625185</v>
+        <v>6625262</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>130080692</v>
       </c>
       <c r="B44" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5233,10 +5233,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130080720</v>
+        <v>130080661</v>
       </c>
       <c r="B45" t="n">
-        <v>56934</v>
+        <v>101109</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5244,21 +5244,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102613</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5268,13 +5268,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>352012</v>
+        <v>351899</v>
       </c>
       <c r="R45" t="n">
-        <v>6625216</v>
+        <v>6625315</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5339,10 +5339,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130080661</v>
+        <v>130080720</v>
       </c>
       <c r="B46" t="n">
-        <v>101022</v>
+        <v>57019</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5350,21 +5350,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>102613</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5374,13 +5374,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>351899</v>
+        <v>352012</v>
       </c>
       <c r="R46" t="n">
-        <v>6625315</v>
+        <v>6625216</v>
       </c>
       <c r="S46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>130080732</v>
       </c>
       <c r="B47" t="n">
-        <v>92961</v>
+        <v>93048</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5551,32 +5551,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130080688</v>
+        <v>130080677</v>
       </c>
       <c r="B48" t="n">
-        <v>92961</v>
+        <v>101109</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5586,10 +5586,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>351946</v>
+        <v>351993</v>
       </c>
       <c r="R48" t="n">
-        <v>6625322</v>
+        <v>6625176</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5657,32 +5657,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130080753</v>
+        <v>130080744</v>
       </c>
       <c r="B49" t="n">
-        <v>57738</v>
+        <v>101109</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5692,13 +5692,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>351938</v>
+        <v>352017</v>
       </c>
       <c r="R49" t="n">
-        <v>6625338</v>
+        <v>6625252</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5763,32 +5763,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130080658</v>
+        <v>130080753</v>
       </c>
       <c r="B50" t="n">
-        <v>80235</v>
+        <v>57823</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5798,13 +5798,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>352098</v>
+        <v>351938</v>
       </c>
       <c r="R50" t="n">
-        <v>6625401</v>
+        <v>6625338</v>
       </c>
       <c r="S50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5869,32 +5869,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130080677</v>
+        <v>130080688</v>
       </c>
       <c r="B51" t="n">
-        <v>101022</v>
+        <v>93048</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5904,10 +5904,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>351993</v>
+        <v>351946</v>
       </c>
       <c r="R51" t="n">
-        <v>6625176</v>
+        <v>6625322</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5975,10 +5975,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130080744</v>
+        <v>130080658</v>
       </c>
       <c r="B52" t="n">
-        <v>101022</v>
+        <v>80320</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>6463</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6010,10 +6010,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>352017</v>
+        <v>352098</v>
       </c>
       <c r="R52" t="n">
-        <v>6625252</v>
+        <v>6625401</v>
       </c>
       <c r="S52" t="n">
         <v>6</v>
@@ -6084,7 +6084,7 @@
         <v>130080680</v>
       </c>
       <c r="B53" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>130080649</v>
       </c>
       <c r="B54" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>130080690</v>
       </c>
       <c r="B55" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6399,32 +6399,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130080748</v>
+        <v>130080711</v>
       </c>
       <c r="B56" t="n">
-        <v>101022</v>
+        <v>93048</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6434,10 +6434,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>351968</v>
+        <v>351948</v>
       </c>
       <c r="R56" t="n">
-        <v>6625362</v>
+        <v>6625339</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6505,32 +6505,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130080711</v>
+        <v>130080748</v>
       </c>
       <c r="B57" t="n">
-        <v>92961</v>
+        <v>101109</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6540,10 +6540,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>351948</v>
+        <v>351968</v>
       </c>
       <c r="R57" t="n">
-        <v>6625339</v>
+        <v>6625362</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6611,32 +6611,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130080698</v>
+        <v>130080652</v>
       </c>
       <c r="B58" t="n">
-        <v>4773</v>
+        <v>93048</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100299</v>
+        <v>5966</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6646,10 +6646,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>351986</v>
+        <v>351953</v>
       </c>
       <c r="R58" t="n">
-        <v>6625378</v>
+        <v>6625320</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6717,32 +6717,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130080652</v>
+        <v>130080747</v>
       </c>
       <c r="B59" t="n">
-        <v>92961</v>
+        <v>101109</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6752,10 +6752,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>351953</v>
+        <v>351963</v>
       </c>
       <c r="R59" t="n">
-        <v>6625320</v>
+        <v>6625354</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6823,10 +6823,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130080747</v>
+        <v>130080724</v>
       </c>
       <c r="B60" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6858,10 +6858,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>351963</v>
+        <v>352010</v>
       </c>
       <c r="R60" t="n">
-        <v>6625354</v>
+        <v>6625223</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6929,10 +6929,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130080724</v>
+        <v>130080698</v>
       </c>
       <c r="B61" t="n">
-        <v>101022</v>
+        <v>4773</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>352010</v>
+        <v>351986</v>
       </c>
       <c r="R61" t="n">
-        <v>6625223</v>
+        <v>6625378</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>

--- a/artfynd/A 59725-2025 artfynd.xlsx
+++ b/artfynd/A 59725-2025 artfynd.xlsx
@@ -2265,32 +2265,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130080673</v>
+        <v>130080718</v>
       </c>
       <c r="B17" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>351941</v>
+        <v>351953</v>
       </c>
       <c r="R17" t="n">
-        <v>6625194</v>
+        <v>6625332</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2371,32 +2371,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130080718</v>
+        <v>130080673</v>
       </c>
       <c r="B18" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>351953</v>
+        <v>351941</v>
       </c>
       <c r="R18" t="n">
-        <v>6625332</v>
+        <v>6625194</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>

--- a/artfynd/A 59725-2025 artfynd.xlsx
+++ b/artfynd/A 59725-2025 artfynd.xlsx
@@ -2053,7 +2053,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130080660</v>
+        <v>130080691</v>
       </c>
       <c r="B15" t="n">
         <v>101109</v>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>351973</v>
+        <v>351862</v>
       </c>
       <c r="R15" t="n">
-        <v>6625359</v>
+        <v>6625186</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2159,7 +2159,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130080691</v>
+        <v>130080660</v>
       </c>
       <c r="B16" t="n">
         <v>101109</v>
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>351862</v>
+        <v>351973</v>
       </c>
       <c r="R16" t="n">
-        <v>6625186</v>
+        <v>6625359</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130080695</v>
+        <v>130080709</v>
       </c>
       <c r="B24" t="n">
-        <v>101109</v>
+        <v>91158</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3018,21 +3018,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>351845</v>
+        <v>351843</v>
       </c>
       <c r="R24" t="n">
-        <v>6625269</v>
+        <v>6625177</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3113,32 +3113,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130080684</v>
+        <v>130080727</v>
       </c>
       <c r="B25" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3148,13 +3148,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>352014</v>
+        <v>351974</v>
       </c>
       <c r="R25" t="n">
-        <v>6625206</v>
+        <v>6625448</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3219,32 +3219,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130080727</v>
+        <v>130080695</v>
       </c>
       <c r="B26" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3254,13 +3254,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>351974</v>
+        <v>351845</v>
       </c>
       <c r="R26" t="n">
-        <v>6625448</v>
+        <v>6625269</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130080653</v>
+        <v>130080684</v>
       </c>
       <c r="B27" t="n">
         <v>101109</v>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>351849</v>
+        <v>352014</v>
       </c>
       <c r="R27" t="n">
-        <v>6625259</v>
+        <v>6625206</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3431,10 +3431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130080709</v>
+        <v>130080653</v>
       </c>
       <c r="B28" t="n">
-        <v>91158</v>
+        <v>101109</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,21 +3442,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4189</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>351843</v>
+        <v>351849</v>
       </c>
       <c r="R28" t="n">
-        <v>6625177</v>
+        <v>6625259</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3537,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130080703</v>
+        <v>130080706</v>
       </c>
       <c r="B29" t="n">
-        <v>40211</v>
+        <v>101109</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3548,21 +3548,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>214803</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>351947</v>
+        <v>351862</v>
       </c>
       <c r="R29" t="n">
-        <v>6625286</v>
+        <v>6625305</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130080689</v>
+        <v>130080703</v>
       </c>
       <c r="B30" t="n">
-        <v>80153</v>
+        <v>40211</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3654,21 +3654,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6441</v>
+        <v>214803</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>352000</v>
+        <v>351947</v>
       </c>
       <c r="R30" t="n">
-        <v>6625332</v>
+        <v>6625286</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3749,10 +3749,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130080706</v>
+        <v>130080689</v>
       </c>
       <c r="B31" t="n">
-        <v>101109</v>
+        <v>80153</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3760,21 +3760,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>6441</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>351862</v>
+        <v>352000</v>
       </c>
       <c r="R31" t="n">
-        <v>6625305</v>
+        <v>6625332</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3855,7 +3855,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130080754</v>
+        <v>130080707</v>
       </c>
       <c r="B32" t="n">
         <v>101109</v>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>351994</v>
+        <v>351988</v>
       </c>
       <c r="R32" t="n">
-        <v>6625214</v>
+        <v>6625206</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3961,7 +3961,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130080743</v>
+        <v>130080659</v>
       </c>
       <c r="B33" t="n">
         <v>101109</v>
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>351863</v>
+        <v>351978</v>
       </c>
       <c r="R33" t="n">
-        <v>6625270</v>
+        <v>6625180</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4067,7 +4067,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130080719</v>
+        <v>130080722</v>
       </c>
       <c r="B34" t="n">
         <v>101109</v>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>351983</v>
+        <v>351871</v>
       </c>
       <c r="R34" t="n">
-        <v>6625356</v>
+        <v>6625188</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4173,32 +4173,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130080705</v>
+        <v>130080746</v>
       </c>
       <c r="B35" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4208,13 +4208,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>351964</v>
+        <v>351961</v>
       </c>
       <c r="R35" t="n">
-        <v>6625310</v>
+        <v>6625364</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130080668</v>
+        <v>130080754</v>
       </c>
       <c r="B36" t="n">
         <v>101109</v>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>352009</v>
+        <v>351994</v>
       </c>
       <c r="R36" t="n">
-        <v>6625177</v>
+        <v>6625214</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4385,7 +4385,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130080707</v>
+        <v>130080743</v>
       </c>
       <c r="B37" t="n">
         <v>101109</v>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>351988</v>
+        <v>351863</v>
       </c>
       <c r="R37" t="n">
-        <v>6625206</v>
+        <v>6625270</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4491,7 +4491,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130080659</v>
+        <v>130080719</v>
       </c>
       <c r="B38" t="n">
         <v>101109</v>
@@ -4526,10 +4526,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>351978</v>
+        <v>351983</v>
       </c>
       <c r="R38" t="n">
-        <v>6625180</v>
+        <v>6625356</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4597,32 +4597,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130080722</v>
+        <v>130080705</v>
       </c>
       <c r="B39" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4632,13 +4632,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>351871</v>
+        <v>351964</v>
       </c>
       <c r="R39" t="n">
-        <v>6625188</v>
+        <v>6625310</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130080746</v>
+        <v>130080668</v>
       </c>
       <c r="B40" t="n">
         <v>101109</v>
@@ -4738,10 +4738,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>351961</v>
+        <v>352009</v>
       </c>
       <c r="R40" t="n">
-        <v>6625364</v>
+        <v>6625177</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4809,7 +4809,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130080700</v>
+        <v>130080692</v>
       </c>
       <c r="B41" t="n">
         <v>101109</v>
@@ -4844,13 +4844,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>351954</v>
+        <v>351814</v>
       </c>
       <c r="R41" t="n">
-        <v>6625185</v>
+        <v>6625310</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4915,10 +4915,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130080731</v>
+        <v>130080700</v>
       </c>
       <c r="B42" t="n">
-        <v>5197</v>
+        <v>101109</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4926,21 +4926,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4950,13 +4950,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>352108</v>
+        <v>351954</v>
       </c>
       <c r="R42" t="n">
-        <v>6625477</v>
+        <v>6625185</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130080702</v>
+        <v>130080731</v>
       </c>
       <c r="B43" t="n">
         <v>5197</v>
@@ -5056,10 +5056,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>352012</v>
+        <v>352108</v>
       </c>
       <c r="R43" t="n">
-        <v>6625262</v>
+        <v>6625477</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5127,10 +5127,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130080692</v>
+        <v>130080702</v>
       </c>
       <c r="B44" t="n">
-        <v>101109</v>
+        <v>5197</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5138,21 +5138,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5162,10 +5162,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>351814</v>
+        <v>352012</v>
       </c>
       <c r="R44" t="n">
-        <v>6625310</v>
+        <v>6625262</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -6611,32 +6611,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130080652</v>
+        <v>130080724</v>
       </c>
       <c r="B58" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6646,10 +6646,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>351953</v>
+        <v>352010</v>
       </c>
       <c r="R58" t="n">
-        <v>6625320</v>
+        <v>6625223</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6717,32 +6717,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130080747</v>
+        <v>130080652</v>
       </c>
       <c r="B59" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6752,10 +6752,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>351963</v>
+        <v>351953</v>
       </c>
       <c r="R59" t="n">
-        <v>6625354</v>
+        <v>6625320</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6823,7 +6823,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130080724</v>
+        <v>130080747</v>
       </c>
       <c r="B60" t="n">
         <v>101109</v>
@@ -6858,10 +6858,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>352010</v>
+        <v>351963</v>
       </c>
       <c r="R60" t="n">
-        <v>6625223</v>
+        <v>6625354</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>

--- a/artfynd/A 59725-2025 artfynd.xlsx
+++ b/artfynd/A 59725-2025 artfynd.xlsx
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130080678</v>
+        <v>130080715</v>
       </c>
       <c r="B7" t="n">
-        <v>101109</v>
+        <v>5197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>351989</v>
+        <v>352047</v>
       </c>
       <c r="R7" t="n">
-        <v>6625211</v>
+        <v>6625255</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130080715</v>
+        <v>130080678</v>
       </c>
       <c r="B9" t="n">
-        <v>5197</v>
+        <v>101109</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1428,21 +1428,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>352047</v>
+        <v>351989</v>
       </c>
       <c r="R9" t="n">
-        <v>6625255</v>
+        <v>6625211</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130080730</v>
+        <v>130080742</v>
       </c>
       <c r="B11" t="n">
-        <v>101109</v>
+        <v>5197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1640,21 +1640,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>351959</v>
+        <v>352129</v>
       </c>
       <c r="R11" t="n">
-        <v>6625368</v>
+        <v>6625324</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130080742</v>
+        <v>130080672</v>
       </c>
       <c r="B12" t="n">
-        <v>5197</v>
+        <v>8440</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>352129</v>
+        <v>351844</v>
       </c>
       <c r="R12" t="n">
-        <v>6625324</v>
+        <v>6625206</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130080672</v>
+        <v>130080730</v>
       </c>
       <c r="B14" t="n">
-        <v>8440</v>
+        <v>101109</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,21 +1958,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>351844</v>
+        <v>351959</v>
       </c>
       <c r="R14" t="n">
-        <v>6625206</v>
+        <v>6625368</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2265,32 +2265,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130080718</v>
+        <v>130080673</v>
       </c>
       <c r="B17" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>351953</v>
+        <v>351941</v>
       </c>
       <c r="R17" t="n">
-        <v>6625332</v>
+        <v>6625194</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2371,32 +2371,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130080673</v>
+        <v>130080718</v>
       </c>
       <c r="B18" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>351941</v>
+        <v>351953</v>
       </c>
       <c r="R18" t="n">
-        <v>6625194</v>
+        <v>6625332</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130080646</v>
+        <v>130080710</v>
       </c>
       <c r="B19" t="n">
-        <v>101109</v>
+        <v>93010</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2488,21 +2488,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>351958</v>
+        <v>351943</v>
       </c>
       <c r="R19" t="n">
-        <v>6625185</v>
+        <v>6625324</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130080710</v>
+        <v>130080646</v>
       </c>
       <c r="B20" t="n">
-        <v>93010</v>
+        <v>101109</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2594,21 +2594,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2618,10 +2618,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>351943</v>
+        <v>351958</v>
       </c>
       <c r="R20" t="n">
-        <v>6625324</v>
+        <v>6625185</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130080695</v>
+        <v>130080653</v>
       </c>
       <c r="B26" t="n">
         <v>101109</v>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>351845</v>
+        <v>351849</v>
       </c>
       <c r="R26" t="n">
-        <v>6625269</v>
+        <v>6625259</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3325,7 +3325,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130080684</v>
+        <v>130080695</v>
       </c>
       <c r="B27" t="n">
         <v>101109</v>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>352014</v>
+        <v>351845</v>
       </c>
       <c r="R27" t="n">
-        <v>6625206</v>
+        <v>6625269</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3431,7 +3431,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130080653</v>
+        <v>130080684</v>
       </c>
       <c r="B28" t="n">
         <v>101109</v>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>351849</v>
+        <v>352014</v>
       </c>
       <c r="R28" t="n">
-        <v>6625259</v>
+        <v>6625206</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3537,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130080706</v>
+        <v>130080703</v>
       </c>
       <c r="B29" t="n">
-        <v>101109</v>
+        <v>40211</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3548,21 +3548,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>214803</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>351862</v>
+        <v>351947</v>
       </c>
       <c r="R29" t="n">
-        <v>6625305</v>
+        <v>6625286</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130080703</v>
+        <v>130080706</v>
       </c>
       <c r="B30" t="n">
-        <v>40211</v>
+        <v>101109</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3654,21 +3654,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>214803</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>351947</v>
+        <v>351862</v>
       </c>
       <c r="R30" t="n">
-        <v>6625286</v>
+        <v>6625305</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3855,32 +3855,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130080707</v>
+        <v>130080705</v>
       </c>
       <c r="B32" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3890,13 +3890,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>351988</v>
+        <v>351964</v>
       </c>
       <c r="R32" t="n">
-        <v>6625206</v>
+        <v>6625310</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130080659</v>
+        <v>130080707</v>
       </c>
       <c r="B33" t="n">
         <v>101109</v>
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>351978</v>
+        <v>351988</v>
       </c>
       <c r="R33" t="n">
-        <v>6625180</v>
+        <v>6625206</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4067,7 +4067,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130080722</v>
+        <v>130080754</v>
       </c>
       <c r="B34" t="n">
         <v>101109</v>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>351871</v>
+        <v>351994</v>
       </c>
       <c r="R34" t="n">
-        <v>6625188</v>
+        <v>6625214</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4173,7 +4173,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130080746</v>
+        <v>130080668</v>
       </c>
       <c r="B35" t="n">
         <v>101109</v>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>351961</v>
+        <v>352009</v>
       </c>
       <c r="R35" t="n">
-        <v>6625364</v>
+        <v>6625177</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4279,7 +4279,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130080754</v>
+        <v>130080722</v>
       </c>
       <c r="B36" t="n">
         <v>101109</v>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>351994</v>
+        <v>351871</v>
       </c>
       <c r="R36" t="n">
-        <v>6625214</v>
+        <v>6625188</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4385,7 +4385,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130080743</v>
+        <v>130080746</v>
       </c>
       <c r="B37" t="n">
         <v>101109</v>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>351863</v>
+        <v>351961</v>
       </c>
       <c r="R37" t="n">
-        <v>6625270</v>
+        <v>6625364</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4597,32 +4597,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130080705</v>
+        <v>130080659</v>
       </c>
       <c r="B39" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4632,13 +4632,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>351964</v>
+        <v>351978</v>
       </c>
       <c r="R39" t="n">
-        <v>6625310</v>
+        <v>6625180</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130080668</v>
+        <v>130080743</v>
       </c>
       <c r="B40" t="n">
         <v>101109</v>
@@ -4738,10 +4738,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>352009</v>
+        <v>351863</v>
       </c>
       <c r="R40" t="n">
-        <v>6625177</v>
+        <v>6625270</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4809,10 +4809,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130080692</v>
+        <v>130080731</v>
       </c>
       <c r="B41" t="n">
-        <v>101109</v>
+        <v>5197</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4844,10 +4844,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>351814</v>
+        <v>352108</v>
       </c>
       <c r="R41" t="n">
-        <v>6625310</v>
+        <v>6625477</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4915,10 +4915,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130080700</v>
+        <v>130080702</v>
       </c>
       <c r="B42" t="n">
-        <v>101109</v>
+        <v>5197</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4926,21 +4926,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4950,13 +4950,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>351954</v>
+        <v>352012</v>
       </c>
       <c r="R42" t="n">
-        <v>6625185</v>
+        <v>6625262</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5021,10 +5021,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130080731</v>
+        <v>130080700</v>
       </c>
       <c r="B43" t="n">
-        <v>5197</v>
+        <v>101109</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5032,21 +5032,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5056,13 +5056,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>352108</v>
+        <v>351954</v>
       </c>
       <c r="R43" t="n">
-        <v>6625477</v>
+        <v>6625185</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5127,10 +5127,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130080702</v>
+        <v>130080692</v>
       </c>
       <c r="B44" t="n">
-        <v>5197</v>
+        <v>101109</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5138,21 +5138,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5162,10 +5162,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>352012</v>
+        <v>351814</v>
       </c>
       <c r="R44" t="n">
-        <v>6625262</v>
+        <v>6625310</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5233,10 +5233,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130080661</v>
+        <v>130080720</v>
       </c>
       <c r="B45" t="n">
-        <v>101109</v>
+        <v>57019</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5244,21 +5244,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>102613</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5268,13 +5268,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>351899</v>
+        <v>352012</v>
       </c>
       <c r="R45" t="n">
-        <v>6625315</v>
+        <v>6625216</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5339,10 +5339,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130080720</v>
+        <v>130080661</v>
       </c>
       <c r="B46" t="n">
-        <v>57019</v>
+        <v>101109</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5350,21 +5350,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102613</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5374,13 +5374,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>352012</v>
+        <v>351899</v>
       </c>
       <c r="R46" t="n">
-        <v>6625216</v>
+        <v>6625315</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130080677</v>
+        <v>130080744</v>
       </c>
       <c r="B48" t="n">
         <v>101109</v>
@@ -5586,13 +5586,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>351993</v>
+        <v>352017</v>
       </c>
       <c r="R48" t="n">
-        <v>6625176</v>
+        <v>6625252</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130080744</v>
+        <v>130080677</v>
       </c>
       <c r="B49" t="n">
         <v>101109</v>
@@ -5692,13 +5692,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>352017</v>
+        <v>351993</v>
       </c>
       <c r="R49" t="n">
-        <v>6625252</v>
+        <v>6625176</v>
       </c>
       <c r="S49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5763,10 +5763,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130080753</v>
+        <v>130080688</v>
       </c>
       <c r="B50" t="n">
-        <v>57823</v>
+        <v>93048</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5774,21 +5774,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5798,10 +5798,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>351938</v>
+        <v>351946</v>
       </c>
       <c r="R50" t="n">
-        <v>6625338</v>
+        <v>6625322</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5869,32 +5869,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130080688</v>
+        <v>130080658</v>
       </c>
       <c r="B51" t="n">
-        <v>93048</v>
+        <v>80320</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5966</v>
+        <v>6463</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5904,13 +5904,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>351946</v>
+        <v>352098</v>
       </c>
       <c r="R51" t="n">
-        <v>6625322</v>
+        <v>6625401</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5975,32 +5975,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130080658</v>
+        <v>130080753</v>
       </c>
       <c r="B52" t="n">
-        <v>80320</v>
+        <v>57823</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6010,13 +6010,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>352098</v>
+        <v>351938</v>
       </c>
       <c r="R52" t="n">
-        <v>6625401</v>
+        <v>6625338</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130080680</v>
+        <v>130080649</v>
       </c>
       <c r="B53" t="n">
         <v>101109</v>
@@ -6116,13 +6116,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>351923</v>
+        <v>351813</v>
       </c>
       <c r="R53" t="n">
-        <v>6625280</v>
+        <v>6625308</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130080649</v>
+        <v>130080690</v>
       </c>
       <c r="B54" t="n">
         <v>101109</v>
@@ -6222,13 +6222,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>351813</v>
+        <v>351880</v>
       </c>
       <c r="R54" t="n">
-        <v>6625308</v>
+        <v>6625196</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130080690</v>
+        <v>130080680</v>
       </c>
       <c r="B55" t="n">
         <v>101109</v>
@@ -6328,13 +6328,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>351880</v>
+        <v>351923</v>
       </c>
       <c r="R55" t="n">
-        <v>6625196</v>
+        <v>6625280</v>
       </c>
       <c r="S55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6611,10 +6611,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130080724</v>
+        <v>130080698</v>
       </c>
       <c r="B58" t="n">
-        <v>101109</v>
+        <v>4773</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6622,21 +6622,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6646,10 +6646,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>352010</v>
+        <v>351986</v>
       </c>
       <c r="R58" t="n">
-        <v>6625223</v>
+        <v>6625378</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6929,10 +6929,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130080698</v>
+        <v>130080724</v>
       </c>
       <c r="B61" t="n">
-        <v>4773</v>
+        <v>101109</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100299</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>351986</v>
+        <v>352010</v>
       </c>
       <c r="R61" t="n">
-        <v>6625378</v>
+        <v>6625223</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>

--- a/artfynd/A 59725-2025 artfynd.xlsx
+++ b/artfynd/A 59725-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130080714</v>
+        <v>130080721</v>
       </c>
       <c r="B2" t="n">
-        <v>101109</v>
+        <v>91692</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>352013</v>
+        <v>351857</v>
       </c>
       <c r="R2" t="n">
-        <v>6625233</v>
+        <v>6625260</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130080721</v>
+        <v>130080714</v>
       </c>
       <c r="B3" t="n">
-        <v>91692</v>
+        <v>101109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>351857</v>
+        <v>352013</v>
       </c>
       <c r="R3" t="n">
-        <v>6625260</v>
+        <v>6625233</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130080737</v>
+        <v>130080644</v>
       </c>
       <c r="B5" t="n">
-        <v>79180</v>
+        <v>4773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>351971</v>
+        <v>352049</v>
       </c>
       <c r="R5" t="n">
-        <v>6625428</v>
+        <v>6625465</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130080644</v>
+        <v>130080737</v>
       </c>
       <c r="B6" t="n">
-        <v>4773</v>
+        <v>79180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>352049</v>
+        <v>351971</v>
       </c>
       <c r="R6" t="n">
-        <v>6625465</v>
+        <v>6625428</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130080742</v>
+        <v>130080665</v>
       </c>
       <c r="B11" t="n">
-        <v>5197</v>
+        <v>101109</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1640,21 +1640,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>352129</v>
+        <v>351806</v>
       </c>
       <c r="R11" t="n">
-        <v>6625324</v>
+        <v>6625305</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130080672</v>
+        <v>130080730</v>
       </c>
       <c r="B12" t="n">
-        <v>8440</v>
+        <v>101109</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>351844</v>
+        <v>351959</v>
       </c>
       <c r="R12" t="n">
-        <v>6625206</v>
+        <v>6625368</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130080665</v>
+        <v>130080672</v>
       </c>
       <c r="B13" t="n">
-        <v>101109</v>
+        <v>8440</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,21 +1852,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>351806</v>
+        <v>351844</v>
       </c>
       <c r="R13" t="n">
-        <v>6625305</v>
+        <v>6625206</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130080730</v>
+        <v>130080742</v>
       </c>
       <c r="B14" t="n">
-        <v>101109</v>
+        <v>5197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,21 +1958,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>351959</v>
+        <v>352129</v>
       </c>
       <c r="R14" t="n">
-        <v>6625368</v>
+        <v>6625324</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2265,32 +2265,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130080673</v>
+        <v>130080718</v>
       </c>
       <c r="B17" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>351941</v>
+        <v>351953</v>
       </c>
       <c r="R17" t="n">
-        <v>6625194</v>
+        <v>6625332</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2371,32 +2371,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130080718</v>
+        <v>130080673</v>
       </c>
       <c r="B18" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>351953</v>
+        <v>351941</v>
       </c>
       <c r="R18" t="n">
-        <v>6625332</v>
+        <v>6625194</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130080709</v>
+        <v>130080653</v>
       </c>
       <c r="B24" t="n">
-        <v>91158</v>
+        <v>101109</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3018,21 +3018,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4189</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>351843</v>
+        <v>351849</v>
       </c>
       <c r="R24" t="n">
-        <v>6625177</v>
+        <v>6625259</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3113,32 +3113,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130080727</v>
+        <v>130080695</v>
       </c>
       <c r="B25" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3148,13 +3148,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>351974</v>
+        <v>351845</v>
       </c>
       <c r="R25" t="n">
-        <v>6625448</v>
+        <v>6625269</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130080653</v>
+        <v>130080684</v>
       </c>
       <c r="B26" t="n">
         <v>101109</v>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>351849</v>
+        <v>352014</v>
       </c>
       <c r="R26" t="n">
-        <v>6625259</v>
+        <v>6625206</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3325,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130080695</v>
+        <v>130080709</v>
       </c>
       <c r="B27" t="n">
-        <v>101109</v>
+        <v>91158</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3336,21 +3336,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>351845</v>
+        <v>351843</v>
       </c>
       <c r="R27" t="n">
-        <v>6625269</v>
+        <v>6625177</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3431,32 +3431,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130080684</v>
+        <v>130080727</v>
       </c>
       <c r="B28" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3466,13 +3466,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>352014</v>
+        <v>351974</v>
       </c>
       <c r="R28" t="n">
-        <v>6625206</v>
+        <v>6625448</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3537,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130080703</v>
+        <v>130080706</v>
       </c>
       <c r="B29" t="n">
-        <v>40211</v>
+        <v>101109</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3548,21 +3548,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>214803</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>351947</v>
+        <v>351862</v>
       </c>
       <c r="R29" t="n">
-        <v>6625286</v>
+        <v>6625305</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130080706</v>
+        <v>130080689</v>
       </c>
       <c r="B30" t="n">
-        <v>101109</v>
+        <v>80153</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3654,21 +3654,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>6441</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>351862</v>
+        <v>352000</v>
       </c>
       <c r="R30" t="n">
-        <v>6625305</v>
+        <v>6625332</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3749,10 +3749,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130080689</v>
+        <v>130080703</v>
       </c>
       <c r="B31" t="n">
-        <v>80153</v>
+        <v>40211</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3760,21 +3760,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6441</v>
+        <v>214803</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>352000</v>
+        <v>351947</v>
       </c>
       <c r="R31" t="n">
-        <v>6625332</v>
+        <v>6625286</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3855,32 +3855,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130080705</v>
+        <v>130080754</v>
       </c>
       <c r="B32" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3890,13 +3890,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>351964</v>
+        <v>351994</v>
       </c>
       <c r="R32" t="n">
-        <v>6625310</v>
+        <v>6625214</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130080754</v>
+        <v>130080659</v>
       </c>
       <c r="B34" t="n">
         <v>101109</v>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>351994</v>
+        <v>351978</v>
       </c>
       <c r="R34" t="n">
-        <v>6625214</v>
+        <v>6625180</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4491,7 +4491,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130080719</v>
+        <v>130080743</v>
       </c>
       <c r="B38" t="n">
         <v>101109</v>
@@ -4526,10 +4526,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>351983</v>
+        <v>351863</v>
       </c>
       <c r="R38" t="n">
-        <v>6625356</v>
+        <v>6625270</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4597,7 +4597,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130080659</v>
+        <v>130080719</v>
       </c>
       <c r="B39" t="n">
         <v>101109</v>
@@ -4632,10 +4632,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>351978</v>
+        <v>351983</v>
       </c>
       <c r="R39" t="n">
-        <v>6625180</v>
+        <v>6625356</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4703,32 +4703,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130080743</v>
+        <v>130080705</v>
       </c>
       <c r="B40" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4738,13 +4738,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>351863</v>
+        <v>351964</v>
       </c>
       <c r="R40" t="n">
-        <v>6625270</v>
+        <v>6625310</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4809,10 +4809,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130080731</v>
+        <v>130080700</v>
       </c>
       <c r="B41" t="n">
-        <v>5197</v>
+        <v>101109</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4844,13 +4844,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>352108</v>
+        <v>351954</v>
       </c>
       <c r="R41" t="n">
-        <v>6625477</v>
+        <v>6625185</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4915,10 +4915,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130080702</v>
+        <v>130080692</v>
       </c>
       <c r="B42" t="n">
-        <v>5197</v>
+        <v>101109</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4926,21 +4926,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4950,10 +4950,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>352012</v>
+        <v>351814</v>
       </c>
       <c r="R42" t="n">
-        <v>6625262</v>
+        <v>6625310</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5021,10 +5021,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130080700</v>
+        <v>130080702</v>
       </c>
       <c r="B43" t="n">
-        <v>101109</v>
+        <v>5197</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5032,21 +5032,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5056,13 +5056,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>351954</v>
+        <v>352012</v>
       </c>
       <c r="R43" t="n">
-        <v>6625185</v>
+        <v>6625262</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5127,10 +5127,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130080692</v>
+        <v>130080731</v>
       </c>
       <c r="B44" t="n">
-        <v>101109</v>
+        <v>5197</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5138,21 +5138,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5162,10 +5162,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>351814</v>
+        <v>352108</v>
       </c>
       <c r="R44" t="n">
-        <v>6625310</v>
+        <v>6625477</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5551,32 +5551,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130080744</v>
+        <v>130080753</v>
       </c>
       <c r="B48" t="n">
-        <v>101109</v>
+        <v>57823</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5586,13 +5586,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>352017</v>
+        <v>351938</v>
       </c>
       <c r="R48" t="n">
-        <v>6625252</v>
+        <v>6625338</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130080677</v>
+        <v>130080744</v>
       </c>
       <c r="B49" t="n">
         <v>101109</v>
@@ -5692,13 +5692,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>351993</v>
+        <v>352017</v>
       </c>
       <c r="R49" t="n">
-        <v>6625176</v>
+        <v>6625252</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5763,32 +5763,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130080688</v>
+        <v>130080677</v>
       </c>
       <c r="B50" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5798,10 +5798,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>351946</v>
+        <v>351993</v>
       </c>
       <c r="R50" t="n">
-        <v>6625322</v>
+        <v>6625176</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5869,32 +5869,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130080658</v>
+        <v>130080688</v>
       </c>
       <c r="B51" t="n">
-        <v>80320</v>
+        <v>93048</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6463</v>
+        <v>5966</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5904,13 +5904,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>352098</v>
+        <v>351946</v>
       </c>
       <c r="R51" t="n">
-        <v>6625401</v>
+        <v>6625322</v>
       </c>
       <c r="S51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5975,32 +5975,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130080753</v>
+        <v>130080658</v>
       </c>
       <c r="B52" t="n">
-        <v>57823</v>
+        <v>80320</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6010,13 +6010,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>351938</v>
+        <v>352098</v>
       </c>
       <c r="R52" t="n">
-        <v>6625338</v>
+        <v>6625401</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6399,32 +6399,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130080711</v>
+        <v>130080748</v>
       </c>
       <c r="B56" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6434,10 +6434,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>351948</v>
+        <v>351968</v>
       </c>
       <c r="R56" t="n">
-        <v>6625339</v>
+        <v>6625362</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6505,32 +6505,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130080748</v>
+        <v>130080711</v>
       </c>
       <c r="B57" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6540,10 +6540,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>351968</v>
+        <v>351948</v>
       </c>
       <c r="R57" t="n">
-        <v>6625362</v>
+        <v>6625339</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6611,10 +6611,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130080698</v>
+        <v>130080747</v>
       </c>
       <c r="B58" t="n">
-        <v>4773</v>
+        <v>101109</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6622,21 +6622,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100299</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6646,10 +6646,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>351986</v>
+        <v>351963</v>
       </c>
       <c r="R58" t="n">
-        <v>6625378</v>
+        <v>6625354</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6717,32 +6717,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130080652</v>
+        <v>130080724</v>
       </c>
       <c r="B59" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6752,10 +6752,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>351953</v>
+        <v>352010</v>
       </c>
       <c r="R59" t="n">
-        <v>6625320</v>
+        <v>6625223</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6823,32 +6823,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130080747</v>
+        <v>130080652</v>
       </c>
       <c r="B60" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6858,10 +6858,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>351963</v>
+        <v>351953</v>
       </c>
       <c r="R60" t="n">
-        <v>6625354</v>
+        <v>6625320</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6929,10 +6929,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130080724</v>
+        <v>130080698</v>
       </c>
       <c r="B61" t="n">
-        <v>101109</v>
+        <v>4773</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>352010</v>
+        <v>351986</v>
       </c>
       <c r="R61" t="n">
-        <v>6625223</v>
+        <v>6625378</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>

--- a/artfynd/A 59725-2025 artfynd.xlsx
+++ b/artfynd/A 59725-2025 artfynd.xlsx
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130080644</v>
+        <v>130080737</v>
       </c>
       <c r="B5" t="n">
-        <v>4773</v>
+        <v>79180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>352049</v>
+        <v>351971</v>
       </c>
       <c r="R5" t="n">
-        <v>6625465</v>
+        <v>6625428</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130080737</v>
+        <v>130080715</v>
       </c>
       <c r="B6" t="n">
-        <v>79180</v>
+        <v>5197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>351971</v>
+        <v>352047</v>
       </c>
       <c r="R6" t="n">
-        <v>6625428</v>
+        <v>6625255</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130080715</v>
+        <v>130080693</v>
       </c>
       <c r="B7" t="n">
-        <v>5197</v>
+        <v>101109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>352047</v>
+        <v>351872</v>
       </c>
       <c r="R7" t="n">
-        <v>6625255</v>
+        <v>6625323</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130080693</v>
+        <v>130080678</v>
       </c>
       <c r="B8" t="n">
         <v>101109</v>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>351872</v>
+        <v>351989</v>
       </c>
       <c r="R8" t="n">
-        <v>6625323</v>
+        <v>6625211</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130080678</v>
+        <v>130080664</v>
       </c>
       <c r="B9" t="n">
         <v>101109</v>
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>351989</v>
+        <v>352009</v>
       </c>
       <c r="R9" t="n">
-        <v>6625211</v>
+        <v>6625188</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130080664</v>
+        <v>130080644</v>
       </c>
       <c r="B10" t="n">
-        <v>101109</v>
+        <v>4773</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1534,21 +1534,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>352009</v>
+        <v>352049</v>
       </c>
       <c r="R10" t="n">
-        <v>6625188</v>
+        <v>6625465</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130080665</v>
+        <v>130080672</v>
       </c>
       <c r="B11" t="n">
-        <v>101109</v>
+        <v>8440</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1640,21 +1640,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>351806</v>
+        <v>351844</v>
       </c>
       <c r="R11" t="n">
-        <v>6625305</v>
+        <v>6625206</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130080730</v>
+        <v>130080742</v>
       </c>
       <c r="B12" t="n">
-        <v>101109</v>
+        <v>5197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>351959</v>
+        <v>352129</v>
       </c>
       <c r="R12" t="n">
-        <v>6625368</v>
+        <v>6625324</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130080672</v>
+        <v>130080665</v>
       </c>
       <c r="B13" t="n">
-        <v>8440</v>
+        <v>101109</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,21 +1852,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>351844</v>
+        <v>351806</v>
       </c>
       <c r="R13" t="n">
-        <v>6625206</v>
+        <v>6625305</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130080742</v>
+        <v>130080730</v>
       </c>
       <c r="B14" t="n">
-        <v>5197</v>
+        <v>101109</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,21 +1958,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>352129</v>
+        <v>351959</v>
       </c>
       <c r="R14" t="n">
-        <v>6625324</v>
+        <v>6625368</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130080653</v>
+        <v>130080709</v>
       </c>
       <c r="B24" t="n">
-        <v>101109</v>
+        <v>91158</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3018,21 +3018,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>351849</v>
+        <v>351843</v>
       </c>
       <c r="R24" t="n">
-        <v>6625259</v>
+        <v>6625177</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3113,7 +3113,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130080695</v>
+        <v>130080653</v>
       </c>
       <c r="B25" t="n">
         <v>101109</v>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>351845</v>
+        <v>351849</v>
       </c>
       <c r="R25" t="n">
-        <v>6625269</v>
+        <v>6625259</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130080684</v>
+        <v>130080695</v>
       </c>
       <c r="B26" t="n">
         <v>101109</v>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>352014</v>
+        <v>351845</v>
       </c>
       <c r="R26" t="n">
-        <v>6625206</v>
+        <v>6625269</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3325,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130080709</v>
+        <v>130080684</v>
       </c>
       <c r="B27" t="n">
-        <v>91158</v>
+        <v>101109</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3336,21 +3336,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4189</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>351843</v>
+        <v>352014</v>
       </c>
       <c r="R27" t="n">
-        <v>6625177</v>
+        <v>6625206</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3537,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130080706</v>
+        <v>130080689</v>
       </c>
       <c r="B29" t="n">
-        <v>101109</v>
+        <v>80153</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3548,21 +3548,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>6441</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>351862</v>
+        <v>352000</v>
       </c>
       <c r="R29" t="n">
-        <v>6625305</v>
+        <v>6625332</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130080689</v>
+        <v>130080706</v>
       </c>
       <c r="B30" t="n">
-        <v>80153</v>
+        <v>101109</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3654,21 +3654,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6441</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>352000</v>
+        <v>351862</v>
       </c>
       <c r="R30" t="n">
-        <v>6625332</v>
+        <v>6625305</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3855,32 +3855,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130080754</v>
+        <v>130080705</v>
       </c>
       <c r="B32" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3890,13 +3890,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>351994</v>
+        <v>351964</v>
       </c>
       <c r="R32" t="n">
-        <v>6625214</v>
+        <v>6625310</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130080659</v>
+        <v>130080754</v>
       </c>
       <c r="B34" t="n">
         <v>101109</v>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>351978</v>
+        <v>351994</v>
       </c>
       <c r="R34" t="n">
-        <v>6625180</v>
+        <v>6625214</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4173,7 +4173,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130080668</v>
+        <v>130080659</v>
       </c>
       <c r="B35" t="n">
         <v>101109</v>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>352009</v>
+        <v>351978</v>
       </c>
       <c r="R35" t="n">
-        <v>6625177</v>
+        <v>6625180</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4279,7 +4279,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130080722</v>
+        <v>130080668</v>
       </c>
       <c r="B36" t="n">
         <v>101109</v>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>351871</v>
+        <v>352009</v>
       </c>
       <c r="R36" t="n">
-        <v>6625188</v>
+        <v>6625177</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4385,7 +4385,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130080746</v>
+        <v>130080722</v>
       </c>
       <c r="B37" t="n">
         <v>101109</v>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>351961</v>
+        <v>351871</v>
       </c>
       <c r="R37" t="n">
-        <v>6625364</v>
+        <v>6625188</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4491,7 +4491,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130080743</v>
+        <v>130080746</v>
       </c>
       <c r="B38" t="n">
         <v>101109</v>
@@ -4526,10 +4526,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>351863</v>
+        <v>351961</v>
       </c>
       <c r="R38" t="n">
-        <v>6625270</v>
+        <v>6625364</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4597,7 +4597,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130080719</v>
+        <v>130080743</v>
       </c>
       <c r="B39" t="n">
         <v>101109</v>
@@ -4632,10 +4632,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>351983</v>
+        <v>351863</v>
       </c>
       <c r="R39" t="n">
-        <v>6625356</v>
+        <v>6625270</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4703,32 +4703,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130080705</v>
+        <v>130080719</v>
       </c>
       <c r="B40" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4738,13 +4738,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>351964</v>
+        <v>351983</v>
       </c>
       <c r="R40" t="n">
-        <v>6625310</v>
+        <v>6625356</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4809,10 +4809,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130080700</v>
+        <v>130080731</v>
       </c>
       <c r="B41" t="n">
-        <v>101109</v>
+        <v>5197</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4844,13 +4844,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>351954</v>
+        <v>352108</v>
       </c>
       <c r="R41" t="n">
-        <v>6625185</v>
+        <v>6625477</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4915,10 +4915,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130080692</v>
+        <v>130080702</v>
       </c>
       <c r="B42" t="n">
-        <v>101109</v>
+        <v>5197</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4926,21 +4926,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4950,10 +4950,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>351814</v>
+        <v>352012</v>
       </c>
       <c r="R42" t="n">
-        <v>6625310</v>
+        <v>6625262</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5021,10 +5021,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130080702</v>
+        <v>130080700</v>
       </c>
       <c r="B43" t="n">
-        <v>5197</v>
+        <v>101109</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5032,21 +5032,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5056,13 +5056,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>352012</v>
+        <v>351954</v>
       </c>
       <c r="R43" t="n">
-        <v>6625262</v>
+        <v>6625185</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5127,10 +5127,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130080731</v>
+        <v>130080692</v>
       </c>
       <c r="B44" t="n">
-        <v>5197</v>
+        <v>101109</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5138,21 +5138,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5162,10 +5162,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>352108</v>
+        <v>351814</v>
       </c>
       <c r="R44" t="n">
-        <v>6625477</v>
+        <v>6625310</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5551,32 +5551,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130080753</v>
+        <v>130080658</v>
       </c>
       <c r="B48" t="n">
-        <v>57823</v>
+        <v>80320</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5586,13 +5586,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>351938</v>
+        <v>352098</v>
       </c>
       <c r="R48" t="n">
-        <v>6625338</v>
+        <v>6625401</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5657,32 +5657,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130080744</v>
+        <v>130080688</v>
       </c>
       <c r="B49" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5692,13 +5692,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>352017</v>
+        <v>351946</v>
       </c>
       <c r="R49" t="n">
-        <v>6625252</v>
+        <v>6625322</v>
       </c>
       <c r="S49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5763,32 +5763,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130080677</v>
+        <v>130080753</v>
       </c>
       <c r="B50" t="n">
-        <v>101109</v>
+        <v>57823</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5798,10 +5798,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>351993</v>
+        <v>351938</v>
       </c>
       <c r="R50" t="n">
-        <v>6625176</v>
+        <v>6625338</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5869,32 +5869,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130080688</v>
+        <v>130080744</v>
       </c>
       <c r="B51" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5904,13 +5904,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>351946</v>
+        <v>352017</v>
       </c>
       <c r="R51" t="n">
-        <v>6625322</v>
+        <v>6625252</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5975,10 +5975,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130080658</v>
+        <v>130080677</v>
       </c>
       <c r="B52" t="n">
-        <v>80320</v>
+        <v>101109</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6463</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6010,13 +6010,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>352098</v>
+        <v>351993</v>
       </c>
       <c r="R52" t="n">
-        <v>6625401</v>
+        <v>6625176</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6399,32 +6399,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130080748</v>
+        <v>130080711</v>
       </c>
       <c r="B56" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6434,10 +6434,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>351968</v>
+        <v>351948</v>
       </c>
       <c r="R56" t="n">
-        <v>6625362</v>
+        <v>6625339</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6505,32 +6505,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130080711</v>
+        <v>130080748</v>
       </c>
       <c r="B57" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6540,10 +6540,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>351948</v>
+        <v>351968</v>
       </c>
       <c r="R57" t="n">
-        <v>6625339</v>
+        <v>6625362</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6611,32 +6611,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130080747</v>
+        <v>130080652</v>
       </c>
       <c r="B58" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6646,10 +6646,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>351963</v>
+        <v>351953</v>
       </c>
       <c r="R58" t="n">
-        <v>6625354</v>
+        <v>6625320</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6717,7 +6717,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130080724</v>
+        <v>130080747</v>
       </c>
       <c r="B59" t="n">
         <v>101109</v>
@@ -6752,10 +6752,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>352010</v>
+        <v>351963</v>
       </c>
       <c r="R59" t="n">
-        <v>6625223</v>
+        <v>6625354</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6823,32 +6823,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130080652</v>
+        <v>130080724</v>
       </c>
       <c r="B60" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6858,10 +6858,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>351953</v>
+        <v>352010</v>
       </c>
       <c r="R60" t="n">
-        <v>6625320</v>
+        <v>6625223</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>

--- a/artfynd/A 59725-2025 artfynd.xlsx
+++ b/artfynd/A 59725-2025 artfynd.xlsx
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130080672</v>
+        <v>130080742</v>
       </c>
       <c r="B11" t="n">
-        <v>8440</v>
+        <v>5197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1640,21 +1640,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>351844</v>
+        <v>352129</v>
       </c>
       <c r="R11" t="n">
-        <v>6625206</v>
+        <v>6625324</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130080742</v>
+        <v>130080672</v>
       </c>
       <c r="B12" t="n">
-        <v>5197</v>
+        <v>8440</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>352129</v>
+        <v>351844</v>
       </c>
       <c r="R12" t="n">
-        <v>6625324</v>
+        <v>6625206</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -5763,10 +5763,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130080658</v>
+        <v>130080744</v>
       </c>
       <c r="B50" t="n">
-        <v>80320</v>
+        <v>101109</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5774,21 +5774,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6463</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5798,10 +5798,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>352098</v>
+        <v>352017</v>
       </c>
       <c r="R50" t="n">
-        <v>6625401</v>
+        <v>6625252</v>
       </c>
       <c r="S50" t="n">
         <v>6</v>
@@ -5869,7 +5869,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130080744</v>
+        <v>130080677</v>
       </c>
       <c r="B51" t="n">
         <v>101109</v>
@@ -5904,13 +5904,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>352017</v>
+        <v>351993</v>
       </c>
       <c r="R51" t="n">
-        <v>6625252</v>
+        <v>6625176</v>
       </c>
       <c r="S51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5975,10 +5975,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130080677</v>
+        <v>130080658</v>
       </c>
       <c r="B52" t="n">
-        <v>101109</v>
+        <v>80320</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>6463</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6010,13 +6010,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>351993</v>
+        <v>352098</v>
       </c>
       <c r="R52" t="n">
-        <v>6625176</v>
+        <v>6625401</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>

--- a/artfynd/A 59725-2025 artfynd.xlsx
+++ b/artfynd/A 59725-2025 artfynd.xlsx
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130080715</v>
+        <v>130080644</v>
       </c>
       <c r="B6" t="n">
-        <v>5197</v>
+        <v>4773</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>352047</v>
+        <v>352049</v>
       </c>
       <c r="R6" t="n">
-        <v>6625255</v>
+        <v>6625465</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130080693</v>
+        <v>130080678</v>
       </c>
       <c r="B7" t="n">
         <v>101109</v>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>351872</v>
+        <v>351989</v>
       </c>
       <c r="R7" t="n">
-        <v>6625323</v>
+        <v>6625211</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130080664</v>
+        <v>130080715</v>
       </c>
       <c r="B8" t="n">
-        <v>101109</v>
+        <v>5197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>352009</v>
+        <v>352047</v>
       </c>
       <c r="R8" t="n">
-        <v>6625188</v>
+        <v>6625255</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130080678</v>
+        <v>130080693</v>
       </c>
       <c r="B9" t="n">
         <v>101109</v>
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>351989</v>
+        <v>351872</v>
       </c>
       <c r="R9" t="n">
-        <v>6625211</v>
+        <v>6625323</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130080644</v>
+        <v>130080664</v>
       </c>
       <c r="B10" t="n">
-        <v>4773</v>
+        <v>101109</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1534,21 +1534,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100299</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>352049</v>
+        <v>352009</v>
       </c>
       <c r="R10" t="n">
-        <v>6625465</v>
+        <v>6625188</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -2265,32 +2265,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130080673</v>
+        <v>130080718</v>
       </c>
       <c r="B17" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>351941</v>
+        <v>351953</v>
       </c>
       <c r="R17" t="n">
-        <v>6625194</v>
+        <v>6625332</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2371,32 +2371,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130080718</v>
+        <v>130080673</v>
       </c>
       <c r="B18" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>351953</v>
+        <v>351941</v>
       </c>
       <c r="R18" t="n">
-        <v>6625332</v>
+        <v>6625194</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130080653</v>
+        <v>130080709</v>
       </c>
       <c r="B24" t="n">
-        <v>101109</v>
+        <v>91158</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3018,21 +3018,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>351849</v>
+        <v>351843</v>
       </c>
       <c r="R24" t="n">
-        <v>6625259</v>
+        <v>6625177</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3113,32 +3113,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130080695</v>
+        <v>130080727</v>
       </c>
       <c r="B25" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3148,13 +3148,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>351845</v>
+        <v>351974</v>
       </c>
       <c r="R25" t="n">
-        <v>6625269</v>
+        <v>6625448</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130080684</v>
+        <v>130080653</v>
       </c>
       <c r="B26" t="n">
         <v>101109</v>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>352014</v>
+        <v>351849</v>
       </c>
       <c r="R26" t="n">
-        <v>6625206</v>
+        <v>6625259</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3325,32 +3325,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130080727</v>
+        <v>130080695</v>
       </c>
       <c r="B27" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3360,13 +3360,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>351974</v>
+        <v>351845</v>
       </c>
       <c r="R27" t="n">
-        <v>6625448</v>
+        <v>6625269</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3431,10 +3431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130080709</v>
+        <v>130080684</v>
       </c>
       <c r="B28" t="n">
-        <v>91158</v>
+        <v>101109</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,21 +3442,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4189</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>351843</v>
+        <v>352014</v>
       </c>
       <c r="R28" t="n">
-        <v>6625177</v>
+        <v>6625206</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>

--- a/artfynd/A 59725-2025 artfynd.xlsx
+++ b/artfynd/A 59725-2025 artfynd.xlsx
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130080644</v>
+        <v>130080715</v>
       </c>
       <c r="B6" t="n">
-        <v>4773</v>
+        <v>5197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100299</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>352049</v>
+        <v>352047</v>
       </c>
       <c r="R6" t="n">
-        <v>6625465</v>
+        <v>6625255</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130080678</v>
+        <v>130080693</v>
       </c>
       <c r="B7" t="n">
         <v>101109</v>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>351989</v>
+        <v>351872</v>
       </c>
       <c r="R7" t="n">
-        <v>6625211</v>
+        <v>6625323</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130080715</v>
+        <v>130080664</v>
       </c>
       <c r="B8" t="n">
-        <v>5197</v>
+        <v>101109</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>352047</v>
+        <v>352009</v>
       </c>
       <c r="R8" t="n">
-        <v>6625255</v>
+        <v>6625188</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130080693</v>
+        <v>130080678</v>
       </c>
       <c r="B9" t="n">
         <v>101109</v>
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>351872</v>
+        <v>351989</v>
       </c>
       <c r="R9" t="n">
-        <v>6625323</v>
+        <v>6625211</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130080664</v>
+        <v>130080644</v>
       </c>
       <c r="B10" t="n">
-        <v>101109</v>
+        <v>4773</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1534,21 +1534,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>352009</v>
+        <v>352049</v>
       </c>
       <c r="R10" t="n">
-        <v>6625188</v>
+        <v>6625465</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130080742</v>
+        <v>130080672</v>
       </c>
       <c r="B11" t="n">
-        <v>5197</v>
+        <v>8440</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1640,21 +1640,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>352129</v>
+        <v>351844</v>
       </c>
       <c r="R11" t="n">
-        <v>6625324</v>
+        <v>6625206</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130080672</v>
+        <v>130080742</v>
       </c>
       <c r="B12" t="n">
-        <v>8440</v>
+        <v>5197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>351844</v>
+        <v>352129</v>
       </c>
       <c r="R12" t="n">
-        <v>6625206</v>
+        <v>6625324</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130080709</v>
+        <v>130080653</v>
       </c>
       <c r="B24" t="n">
-        <v>91158</v>
+        <v>101109</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3018,21 +3018,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4189</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>351843</v>
+        <v>351849</v>
       </c>
       <c r="R24" t="n">
-        <v>6625177</v>
+        <v>6625259</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3113,32 +3113,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130080727</v>
+        <v>130080695</v>
       </c>
       <c r="B25" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3148,13 +3148,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>351974</v>
+        <v>351845</v>
       </c>
       <c r="R25" t="n">
-        <v>6625448</v>
+        <v>6625269</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130080653</v>
+        <v>130080684</v>
       </c>
       <c r="B26" t="n">
         <v>101109</v>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>351849</v>
+        <v>352014</v>
       </c>
       <c r="R26" t="n">
-        <v>6625259</v>
+        <v>6625206</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3325,32 +3325,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130080695</v>
+        <v>130080727</v>
       </c>
       <c r="B27" t="n">
-        <v>101109</v>
+        <v>93048</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3360,13 +3360,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>351845</v>
+        <v>351974</v>
       </c>
       <c r="R27" t="n">
-        <v>6625269</v>
+        <v>6625448</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3431,10 +3431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130080684</v>
+        <v>130080709</v>
       </c>
       <c r="B28" t="n">
-        <v>101109</v>
+        <v>91158</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,21 +3442,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>352014</v>
+        <v>351843</v>
       </c>
       <c r="R28" t="n">
-        <v>6625206</v>
+        <v>6625177</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -5763,10 +5763,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130080744</v>
+        <v>130080658</v>
       </c>
       <c r="B50" t="n">
-        <v>101109</v>
+        <v>80320</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5774,21 +5774,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>6463</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5798,10 +5798,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>352017</v>
+        <v>352098</v>
       </c>
       <c r="R50" t="n">
-        <v>6625252</v>
+        <v>6625401</v>
       </c>
       <c r="S50" t="n">
         <v>6</v>
@@ -5869,7 +5869,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130080677</v>
+        <v>130080744</v>
       </c>
       <c r="B51" t="n">
         <v>101109</v>
@@ -5904,13 +5904,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>351993</v>
+        <v>352017</v>
       </c>
       <c r="R51" t="n">
-        <v>6625176</v>
+        <v>6625252</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5975,10 +5975,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130080658</v>
+        <v>130080677</v>
       </c>
       <c r="B52" t="n">
-        <v>80320</v>
+        <v>101109</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6463</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6010,13 +6010,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>352098</v>
+        <v>351993</v>
       </c>
       <c r="R52" t="n">
-        <v>6625401</v>
+        <v>6625176</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6611,32 +6611,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130080698</v>
+        <v>130080652</v>
       </c>
       <c r="B58" t="n">
-        <v>4773</v>
+        <v>93048</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100299</v>
+        <v>5966</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6646,10 +6646,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>351986</v>
+        <v>351953</v>
       </c>
       <c r="R58" t="n">
-        <v>6625378</v>
+        <v>6625320</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6717,10 +6717,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130080724</v>
+        <v>130080698</v>
       </c>
       <c r="B59" t="n">
-        <v>101109</v>
+        <v>4773</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6728,21 +6728,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6752,10 +6752,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>352010</v>
+        <v>351986</v>
       </c>
       <c r="R59" t="n">
-        <v>6625223</v>
+        <v>6625378</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6823,32 +6823,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130080652</v>
+        <v>130080724</v>
       </c>
       <c r="B60" t="n">
-        <v>93048</v>
+        <v>101109</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6858,10 +6858,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>351953</v>
+        <v>352010</v>
       </c>
       <c r="R60" t="n">
-        <v>6625320</v>
+        <v>6625223</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
